--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$122</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4522" uniqueCount="631">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1242,10 +1242,31 @@
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>RF1-5</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="INT"].code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category:imagerie</t>
+  </si>
+  <si>
+    <t>imagerie</t>
+  </si>
+  <si>
+    <t>Catégorie de la demande d'examen d'imagerie</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="363679005"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>ServiceRequest.priority</t>
@@ -1313,7 +1334,7 @@
 </t>
   </si>
   <si>
-    <t>Type de la demande : Si aucun code n'est trouvé dans des terminologies existantes, utiliser le code : GEN-092.04.20 'Autre demande d’examen ou de suivi'</t>
+    <t>Examen d'imagerie prescrit</t>
   </si>
   <si>
     <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
@@ -1322,10 +1343,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred].</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-document-imagerie-cisis|20260716085851</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1775,6 +1793,111 @@
     <t>.outboundRelationship[typeCode=PERT].target</t>
   </si>
   <si>
+    <t>ServiceRequest.supportingInfo.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.supportingInfo.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.supportingInfo.extension:codeableConcept</t>
+  </si>
+  <si>
+    <t>codeableConcept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-ServiceRequest.supportingInfo|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>R5: supportingInfo additional types</t>
+  </si>
+  <si>
+    <t>R5: `ServiceRequest.supportingInfo` additional types (CodeableReference(http://hl7.org/fhir/StructureDefinition/Resource)) additional types from child elements (concept)</t>
+  </si>
+  <si>
+    <t>Element `ServiceRequest.supportingInfo` is mapped to FHIR R4 element `ServiceRequest.supportingInfo` as `SourceIsBroaderThanTarget`.
+The mappings for `ServiceRequest.supportingInfo` do not cover the following types: CodeableReference.
+The mappings for `ServiceRequest.supportingInfo` do not cover the following types based on type expansion: concept.
+To represent information about how the services are to be delivered use the `instructions` element.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.supportingInfo.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.supportingInfo.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>ServiceRequest.supportingInfo.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.supportingInfo.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>ServiceRequest.specimen</t>
   </si>
   <si>
@@ -1814,9 +1937,6 @@
   </si>
   <si>
     <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
@@ -2200,7 +2320,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO114"/>
+  <dimension ref="A1:AO122"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="74.65234375" customWidth="true" bestFit="true"/>
@@ -2227,7 +2347,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="160.17578125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="108.3203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -12614,7 +12734,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
         <v>383</v>
       </c>
@@ -12627,7 +12747,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>80</v>
@@ -12691,16 +12811,14 @@
         <v>81</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="AC90" s="2"/>
       <c r="AD90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>383</v>
@@ -12721,10 +12839,10 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>382</v>
@@ -12733,26 +12851,28 @@
         <v>81</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>81</v>
@@ -12761,27 +12881,29 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q91" t="s" s="2">
-        <v>396</v>
-      </c>
+      <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>81</v>
+        <v>397</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>81</v>
@@ -12796,13 +12918,13 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>182</v>
+        <v>388</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -12820,13 +12942,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>81</v>
@@ -12835,16 +12957,16 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>399</v>
+        <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -12852,10 +12974,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12872,31 +12994,27 @@
         <v>81</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>404</v>
+        <v>110</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q92" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="R92" t="s" s="2">
         <v>81</v>
@@ -12917,13 +13035,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>81</v>
+        <v>402</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -12941,7 +13059,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12956,65 +13074,69 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I93" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>192</v>
+        <v>409</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q93" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
         <v>81</v>
       </c>
@@ -13034,13 +13156,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -13058,7 +13180,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13073,38 +13195,38 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>91</v>
@@ -13119,13 +13241,13 @@
         <v>192</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13151,13 +13273,11 @@
         <v>81</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>81</v>
@@ -13175,56 +13295,56 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>81</v>
+        <v>426</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>81</v>
@@ -13233,18 +13353,18 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>434</v>
+        <v>192</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13268,13 +13388,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13292,16 +13412,16 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>102</v>
@@ -13310,24 +13430,24 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>81</v>
+        <v>427</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13335,7 +13455,7 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>90</v>
@@ -13350,16 +13470,18 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13407,10 +13529,10 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>90</v>
@@ -13422,35 +13544,35 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>443</v>
+        <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>90</v>
@@ -13465,13 +13587,13 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13522,10 +13644,10 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>90</v>
@@ -13537,41 +13659,41 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>81</v>
@@ -13580,13 +13702,13 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13637,7 +13759,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13652,41 +13774,41 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>81</v>
@@ -13695,13 +13817,13 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13728,13 +13850,13 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>472</v>
+        <v>81</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -13752,7 +13874,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13767,31 +13889,31 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>81</v>
+        <v>467</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>81</v>
+        <v>470</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>477</v>
+        <v>81</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -13810,13 +13932,13 @@
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13843,13 +13965,13 @@
         <v>81</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>81</v>
+        <v>477</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -13867,7 +13989,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13882,31 +14004,31 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>481</v>
+        <v>81</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>484</v>
+        <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -13916,7 +14038,7 @@
         <v>90</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>81</v>
@@ -13925,17 +14047,15 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -13984,7 +14104,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13999,31 +14119,31 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14033,7 +14153,7 @@
         <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>81</v>
@@ -14042,16 +14162,16 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>192</v>
+        <v>492</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14077,13 +14197,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14101,7 +14221,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14116,38 +14236,38 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>81</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>81</v>
@@ -14159,16 +14279,16 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>510</v>
+        <v>192</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14194,13 +14314,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14218,13 +14338,13 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>81</v>
@@ -14233,16 +14353,16 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14250,14 +14370,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14276,15 +14396,17 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>192</v>
+        <v>514</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14309,13 +14431,13 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>520</v>
+        <v>81</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>521</v>
+        <v>81</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14333,7 +14455,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14348,16 +14470,16 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>81</v>
+        <v>518</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -14365,10 +14487,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14391,13 +14513,13 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>524</v>
+        <v>192</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14424,13 +14546,13 @@
         <v>81</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>81</v>
+        <v>524</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>81</v>
+        <v>525</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>81</v>
@@ -14448,7 +14570,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14472,7 +14594,7 @@
         <v>526</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>81</v>
@@ -14506,17 +14628,15 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>192</v>
+        <v>528</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N106" t="s" s="2">
-        <v>530</v>
-      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -14541,13 +14661,13 @@
         <v>81</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>531</v>
+        <v>81</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>532</v>
+        <v>81</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
@@ -14580,16 +14700,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>533</v>
+        <v>81</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>534</v>
+        <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>81</v>
@@ -14597,10 +14717,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14623,16 +14743,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>538</v>
+        <v>192</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14658,13 +14778,13 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>81</v>
+        <v>535</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>81</v>
+        <v>536</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -14682,7 +14802,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14697,16 +14817,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>81</v>
@@ -14714,10 +14834,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14737,18 +14857,20 @@
         <v>81</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -14797,7 +14919,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14812,16 +14934,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>81</v>
+        <v>540</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>81</v>
@@ -14829,14 +14951,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>553</v>
+        <v>81</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14855,17 +14977,15 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -14914,7 +15034,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14929,13 +15049,13 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -14946,14 +15066,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>81</v>
+        <v>557</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -14969,19 +15089,19 @@
         <v>81</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15031,7 +15151,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15046,13 +15166,13 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
@@ -15061,48 +15181,44 @@
         <v>81</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>570</v>
+        <v>156</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>81</v>
       </c>
@@ -15126,11 +15242,13 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>575</v>
+        <v>81</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -15148,46 +15266,46 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>568</v>
+        <v>158</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="AM111" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>578</v>
-      </c>
       <c r="B112" t="s" s="2">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15197,7 +15315,7 @@
         <v>80</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>81</v>
@@ -15206,15 +15324,17 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>579</v>
+        <v>135</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>580</v>
+        <v>224</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15251,19 +15371,19 @@
         <v>81</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>578</v>
+        <v>164</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15275,32 +15395,34 @@
         <v>81</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>582</v>
+        <v>81</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>583</v>
+        <v>159</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>584</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="C113" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="D113" t="s" s="2">
         <v>81</v>
       </c>
@@ -15309,7 +15431,7 @@
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>81</v>
@@ -15318,18 +15440,20 @@
         <v>81</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>155</v>
+        <v>569</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15378,28 +15502,28 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>585</v>
+        <v>164</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>588</v>
+        <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -15410,10 +15534,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15424,7 +15548,7 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>81</v>
@@ -15433,19 +15557,19 @@
         <v>81</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>590</v>
+        <v>155</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15495,38 +15619,970 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>81</v>
+        <v>578</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="AL114" t="s" s="2">
+      <c r="N117" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM117" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM114" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO114" t="s" s="2">
+      <c r="AN117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="Y119" s="2"/>
+      <c r="Z119" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO122" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO114">
+  <autoFilter ref="A1:AO122">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15536,7 +16592,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI121">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1343,7 +1343,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-document-imagerie-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-document-imagerie-cisis|20260916095453</t>
   </si>
   <si>
     <t>Request.code</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
